--- a/sheets/민요/검수/노래가락.xlsx
+++ b/sheets/민요/검수/노래가락.xlsx
@@ -498,7 +498,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -507,17 +507,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -542,6 +542,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
@@ -637,7 +643,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -683,6 +689,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3990,594 +4028,594 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="13" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="9" t="s">
+      <c r="J3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="9" t="s">
+      <c r="L3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="9"/>
+      <c r="O3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="10" t="s">
+      <c r="J4" s="15"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="10"/>
+      <c r="O4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="I5" s="17"/>
+      <c r="J5" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="17" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="D6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="11" t="s">
+      <c r="J6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="18" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="16"/>
+      <c r="H7" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="16"/>
+      <c r="J7" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="8" t="s">
+      <c r="K7" s="16"/>
+      <c r="L7" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="O7" s="9"/>
+      <c r="O7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="O8" s="10" t="s">
+      <c r="N8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O8" s="17" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="N9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="O9" s="10" t="s">
+      <c r="N9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="18"/>
+      <c r="D10" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="18"/>
+      <c r="F10" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="18"/>
+      <c r="J10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="8" t="s">
+      <c r="K10" s="18"/>
+      <c r="L10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="8" t="s">
+      <c r="M10" s="18"/>
+      <c r="N10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="O11" s="9"/>
+      <c r="N11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
+      <c r="G12" s="19"/>
+      <c r="H12" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="O12" s="8"/>
+      <c r="O12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="8" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="8" t="s">
+      <c r="E13" s="17"/>
+      <c r="F13" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="O13" s="10"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="8" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="O14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="8" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="16"/>
+      <c r="H15" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="8" t="s">
+      <c r="K15" s="16"/>
+      <c r="L15" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="8" t="s">
+      <c r="N15" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="O15" s="9"/>
+      <c r="O15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="8" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="8" t="s">
+      <c r="H16" s="15"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="10"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="8" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="8" t="s">
+      <c r="G17" s="17"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="10"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="11"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/노래가락.xlsx
+++ b/sheets/민요/검수/노래가락.xlsx
@@ -567,10 +567,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/노래가락.xlsx
+++ b/sheets/민요/검수/노래가락.xlsx
@@ -4019,7 +4019,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:O18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -4041,8 +4041,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="13" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -4060,7 +4060,7 @@
       <c r="N2" s="14"/>
       <c r="O2" s="14"/>
     </row>
-    <row r="3" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B3" s="15" t="s">
         <v>58</v>
       </c>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B4" s="15" t="s">
         <v>57</v>
       </c>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="O4" s="17"/>
     </row>
-    <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B5" s="15" t="s">
         <v>118</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B6" s="15" t="s">
         <v>47</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="O7" s="16"/>
     </row>
-    <row r="8" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B8" s="15" t="s">
         <v>47</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B9" s="15" t="s">
         <v>55</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B10" s="15" t="s">
         <v>58</v>
       </c>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="O10" s="18"/>
     </row>
-    <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B11" s="15" t="s">
         <v>57</v>
       </c>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="O11" s="16"/>
     </row>
-    <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B12" s="15" t="s">
         <v>76</v>
       </c>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B13" s="15"/>
       <c r="C13" s="17"/>
       <c r="D13" s="15" t="s">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="O13" s="17"/>
     </row>
-    <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B14" s="15"/>
       <c r="C14" s="18"/>
       <c r="D14" s="15"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O14" s="18"/>
     </row>
-    <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B15" s="15"/>
       <c r="C15" s="16"/>
       <c r="D15" s="15"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O15" s="16"/>
     </row>
-    <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B16" s="15"/>
       <c r="C16" s="17"/>
       <c r="D16" s="15"/>
@@ -4574,7 +4574,7 @@
       <c r="N16" s="15"/>
       <c r="O16" s="17"/>
     </row>
-    <row r="17" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B17" s="15"/>
       <c r="C17" s="17"/>
       <c r="D17" s="15"/>
@@ -4596,7 +4596,7 @@
       <c r="N17" s="15"/>
       <c r="O17" s="17"/>
     </row>
-    <row r="18" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
       <c r="B18" s="15"/>
       <c r="C18" s="18"/>
       <c r="D18" s="15"/>
@@ -4620,7 +4620,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/노래가락.xlsx
+++ b/sheets/민요/검수/노래가락.xlsx
@@ -4025,24 +4025,24 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="13" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="57.14" customHeight="true">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -4060,7 +4060,7 @@
       <c r="N2" s="14"/>
       <c r="O2" s="14"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B3" s="15" t="s">
         <v>58</v>
       </c>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B4" s="15" t="s">
         <v>57</v>
       </c>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="O4" s="17"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B5" s="15" t="s">
         <v>118</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B6" s="15" t="s">
         <v>47</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="O7" s="16"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B8" s="15" t="s">
         <v>47</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B9" s="15" t="s">
         <v>55</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B10" s="15" t="s">
         <v>58</v>
       </c>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="O10" s="18"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B11" s="15" t="s">
         <v>57</v>
       </c>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="O11" s="16"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B12" s="15" t="s">
         <v>76</v>
       </c>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B13" s="15"/>
       <c r="C13" s="17"/>
       <c r="D13" s="15" t="s">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="O13" s="17"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B14" s="15"/>
       <c r="C14" s="18"/>
       <c r="D14" s="15"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O14" s="18"/>
     </row>
-    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B15" s="15"/>
       <c r="C15" s="16"/>
       <c r="D15" s="15"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O15" s="16"/>
     </row>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B16" s="15"/>
       <c r="C16" s="17"/>
       <c r="D16" s="15"/>
@@ -4574,7 +4574,7 @@
       <c r="N16" s="15"/>
       <c r="O16" s="17"/>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B17" s="15"/>
       <c r="C17" s="17"/>
       <c r="D17" s="15"/>
@@ -4596,7 +4596,7 @@
       <c r="N17" s="15"/>
       <c r="O17" s="17"/>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="67.65" customHeight="true">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
       <c r="B18" s="15"/>
       <c r="C18" s="18"/>
       <c r="D18" s="15"/>
@@ -4620,7 +4620,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
